--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -616,14 +616,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -718,10 +718,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -734,7 +734,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -745,7 +745,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -754,7 +754,7 @@
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="20" customWidth="1" min="49" max="49"/>
     <col width="16" customWidth="1" min="50" max="50"/>
@@ -1079,10 +1079,8 @@
           <t>Dinesh Shrestha</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9851056329</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9851056329</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1095,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9851056329</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9851056329</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1168,10 +1164,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -1182,35 +1176,239 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>21h 50m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX2" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 9:35 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335765</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>M.d  talibakhtar</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>M.d  talibakhtar</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9810170827</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:35:00 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9810170827</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:31:48 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:35:00 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>27.71201, 85.33701, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB024</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>21h 50m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 3m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AW2" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX2" s="3" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -572,10 +572,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -612,23 +612,46 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>WiFi 6 Upgrade</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -675,10 +698,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -688,10 +711,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -716,7 +739,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -756,7 +779,7 @@
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="16" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1277,10 +1300,8 @@
           <t>M.d  talibakhtar</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9810170827</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9810170827</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1295,10 +1316,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9810170827</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9810170827</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1348,10 +1367,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH3" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI3" s="3" t="inlineStr"/>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1366,10 +1383,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1380,35 +1395,239 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 3m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 9:56 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336839</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Samyog oli</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Samyog oli</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9841565677</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:56:32 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9841565677</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 03:09:32 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:56:32 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Maitidevi ghatekulo shikari gali, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>04:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>1d 19h 3m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr">
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>18h 47m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -728,11 +728,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -741,10 +741,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="25" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -758,11 +758,11 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="25" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="26" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1496,10 +1496,8 @@
           <t>Samyog oli</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9841565677</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9841565677</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1514,10 +1512,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9841565677</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9841565677</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1585,10 +1581,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1599,35 +1593,459 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>18h 47m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:10 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337429</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Prabin shrestha</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Prabin shrestha</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9823138733</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:39:31 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9823138733</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:39:31 AM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:10:22 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.694908</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>near KUNDAN STORE AND WINE SHOP Tri-Netra Tole, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>ps588355@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L38-1</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.34301</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>30m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>30m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:06 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336711</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Air Care Service Center</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Bandan Sampang Rai</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9807951781</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:14:11 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9807951781</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 01:26:48 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:14:11 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.73474</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Rato Pul - Bridge P85P+6PG Pashupati Sadak Kathmandu 44600, , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>bandan.kirati@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Yaman Bhandari</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L5-1</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.35697</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>18h 47m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>20h 47m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,36 +528,72 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>40.0%</t>
+      <c r="B5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -616,19 +652,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -639,19 +675,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -666,12 +702,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -682,10 +720,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -698,23 +746,54 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C2" s="6" t="n">
-        <v>5</v>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>5</v>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -728,25 +807,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="25" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -756,7 +835,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="25" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -768,8 +847,8 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -780,7 +859,7 @@
     <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1694,10 +1773,8 @@
           <t>Prabin shrestha</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9823138733</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9823138733</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1712,10 +1789,8 @@
       </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>9823138733</t>
-        </is>
+      <c r="U5" s="3" t="n">
+        <v>9823138733</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1732,10 +1807,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.694908</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.694908</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1787,25 +1860,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L38-1</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.34301</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.34301000000001</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1906,10 +1975,8 @@
           <t>Bandan Sampang Rai</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9807951781</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9807951781</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1924,10 +1991,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>9807951781</t>
-        </is>
+      <c r="U6" s="3" t="n">
+        <v>9807951781</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1944,10 +2009,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.73474</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.73474</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1999,55 +2062,475 @@
           <t>Yaman Bhandari</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L5-1</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.35697</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.35697</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>20h 47m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:17 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336682</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Singh</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Prabin Singh</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9841386725</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:17:30 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9841386725</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 12:59:39 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:17:30 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.66188</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>M862+GQ7, Aadinath Marg, Karyabinayak,Near by Sumi Carpet Manufacturer, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>07:18 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB268</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.29778</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>20h 47m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW6" s="3" t="inlineStr">
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>21h 17m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX6" s="3" t="inlineStr">
-        <is>
-          <t>Sabin Giri</t>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:35 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336457</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Prajapati</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Prajapati</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9841972051</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 10:26:16 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9841972051</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 10:20:17 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:35:11 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.677836</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Bhatkya Pati Gift Shop - Gift shop MCHV+Q2H Bhaktapur 44800, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>Jay.sanpjpt@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L15-5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.443087</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 8m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -580,20 +580,38 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>42.9%</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -664,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -675,19 +693,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -702,14 +720,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,6 +754,11 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -749,19 +773,22 @@
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>6</v>
+      <c r="E2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -771,29 +798,57 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="C5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>7</v>
+      <c r="E5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -807,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -823,7 +878,7 @@
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -841,7 +896,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="26" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="26" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -2177,10 +2232,8 @@
           <t>Prabin Singh</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9841386725</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9841386725</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2195,10 +2248,8 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>9841386725</t>
-        </is>
+      <c r="U7" s="3" t="n">
+        <v>9841386725</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -2215,10 +2266,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.66188</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.66188</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2270,25 +2319,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>CDB268</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.29778</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.29778</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2389,10 +2434,8 @@
           <t>Sanjay Prajapati</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9841972051</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9841972051</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2407,10 +2450,8 @@
       </c>
       <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr"/>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>9841972051</t>
-        </is>
+      <c r="U8" s="3" t="n">
+        <v>9841972051</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -2427,10 +2468,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.677836</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.677836</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2482,55 +2521,1443 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L15-5</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.443087</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.44308700000001</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>1d 8m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>1d 8m</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>1d 14m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:40 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335308</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 04:10:11 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 08:59:52 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:40:42 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.7709</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Hello Kids Academy Montessori School Details from Google Maps Q9C3+32Q, Budhanilkantha 44600 , Bagma</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>pokharelnaba1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L15-8</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.3504</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>18h 30m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 40m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:36 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336711</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Air Care Service Center</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Bandan Sampang Rai</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9807951781</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX8" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:14:11 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9807951781</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 01:26:48 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:36:58 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.73474</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Rato Pul - Bridge P85P+6PG Pashupati Sadak Kathmandu 44600, , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>bandan.kirati@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L5-1</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.35697</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>22m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>21h 10m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:34 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337421</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Binod Ojha</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Binod Ojha</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841193727</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:34:39 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9841193727</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:28:36 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:34:39 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.71377</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Baking Flower Details from Google Maps kharibot sarkaridhara, Kathmandu 44600 +977 984-1448343, Bagm</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>binodojha100@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>00:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Maharjan</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L18-4</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.34661</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>1h 6m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:42 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336304</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Suroj Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Suroj Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9810284042</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 07:36:29 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9808822732</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 07:36:29 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:42:38 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.677433</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>27.677433, 85.239541, Near by bouthali chowk, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>10:42 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB250</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.239541</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 6m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 6m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:41 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:39 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335865</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Kumar Manandhar</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Kumar Manandhar</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9851223690</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:40:08 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9851223690</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:40:08 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:39:39 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.682156</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Satungal -07 Kathmandu Tribhuvan Highway 07 Chandragiri,Near Dhaulagiri Aawas Samaj , Bagmati, Centr</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>nhuja.manandhar524@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>14:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB237</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.24531</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 59m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 59m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:38 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335865</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Kumar Manandhar</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Kumar Manandhar</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9851223690</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:40:08 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9851223690</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:40:08 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:39:39 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.682156</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Satungal -07 Kathmandu Tribhuvan Highway 07 Chandragiri,Near Dhaulagiri Aawas Samaj , Bagmati, Centr</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>nhuja.manandhar524@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>14:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB237</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.24531</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 59m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 59m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,90 +528,108 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="B7" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -693,19 +711,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -720,15 +738,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -739,25 +758,30 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -770,29 +794,32 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F2" s="6" t="n">
-        <v>10</v>
+      <c r="G2" s="6" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
@@ -801,16 +828,19 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -820,35 +850,66 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>12</v>
+      <c r="G6" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -862,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -873,7 +934,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -897,12 +958,12 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -2636,10 +2697,8 @@
           <t>Nabaraj Pokharel</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9851042928</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9851042928</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2654,10 +2713,8 @@
       </c>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>9851042928</t>
-        </is>
+      <c r="U9" s="3" t="n">
+        <v>9851042928</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -2674,10 +2731,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.7709</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.7709</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2729,25 +2784,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L15-8</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.3504</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.35039999999999</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2848,10 +2899,8 @@
           <t>Bandan Sampang Rai</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9807951781</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9807951781</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2866,10 +2915,8 @@
       </c>
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr"/>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>9807951781</t>
-        </is>
+      <c r="U10" s="3" t="n">
+        <v>9807951781</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2886,10 +2933,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.73474</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.73474</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2941,25 +2986,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L5-1</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.35697</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.35697</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3060,10 +3101,8 @@
           <t>Binod Ojha</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841193727</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841193727</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3078,10 +3117,8 @@
       </c>
       <c r="S11" s="3" t="inlineStr"/>
       <c r="T11" s="3" t="inlineStr"/>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>9841193727</t>
-        </is>
+      <c r="U11" s="3" t="n">
+        <v>9841193727</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -3098,10 +3135,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.71377</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.71377</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3157,25 +3192,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L18-4</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.34661</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.34661</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -3276,10 +3307,8 @@
           <t>Suroj Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9810284042</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9810284042</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3294,10 +3323,8 @@
       </c>
       <c r="S12" s="3" t="inlineStr"/>
       <c r="T12" s="3" t="inlineStr"/>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>9808822732</t>
-        </is>
+      <c r="U12" s="3" t="n">
+        <v>9808822732</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -3314,10 +3341,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.677433</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.677433</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3369,25 +3394,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB250</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.239541</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.239541</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
@@ -3596,10 +3617,8 @@
           <t>Suresh Kumar Manandhar</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9851223690</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9851223690</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3614,10 +3633,8 @@
       </c>
       <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>9851223690</t>
-        </is>
+      <c r="U14" s="3" t="n">
+        <v>9851223690</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -3634,10 +3651,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.682156</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.682156</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3693,25 +3708,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>CDB237</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.24531</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.24531</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3812,10 +3823,8 @@
           <t>Suresh Kumar Manandhar</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9851223690</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9851223690</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3830,10 +3839,8 @@
       </c>
       <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="inlineStr"/>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>9851223690</t>
-        </is>
+      <c r="U15" s="3" t="n">
+        <v>9851223690</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -3850,10 +3857,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.682156</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.682156</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3909,47 +3914,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>CDB237</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.24531</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.24531</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 59m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 59m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>1d 18h 59m</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>1d 18h 59m</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -3958,6 +3959,878 @@
       <c r="AX15" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335979</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Palcha newari kitchen</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Palcha newari kitchen</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9860489010</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:27:29 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9860489010</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:21:22 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:27:29 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.67179</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Jawalakhel Paalcha Newari kitchen, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>leejen73@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>14:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>2,9</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.31512</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 6m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:21 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336901</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Surya Gubaju</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Surya Gubaju</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9851337513</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:15:22 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 10: 15:00 AM</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9851337513</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 04:15:19 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:21:48 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.702449</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>27.702283, 85.308809, nearVishal Bazar - Shopping mall, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>05:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr">
+        <is>
+          <t>18:44 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>CDB181</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.312103</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>19h 6m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:30 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337405</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Suyogya Bhandari</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Suyogya Bhandari</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9801056282</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:30:36 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9801056282</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:17:36 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:30:36 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.734477</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Deurali-Janta Pharma OfficeP8VR+XW7, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>suyogyaca@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>01:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L3-6</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.338261</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>2h 13m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:20 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337405</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Suyogya Bhandari</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Suyogya Bhandari</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9801056282</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:30:36 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9801056282</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:17:36 AM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:30:36 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.734477</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Deurali-Janta Pharma OfficeP8VR+XW7, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>suyogyaca@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>01:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L3-6</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.338261</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2h 13m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -969,7 +969,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4029,10 +4029,8 @@
           <t>Palcha newari kitchen</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9860489010</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9860489010</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4047,10 +4045,8 @@
       </c>
       <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="inlineStr"/>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>9860489010</t>
-        </is>
+      <c r="U16" s="3" t="n">
+        <v>9860489010</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -4067,10 +4063,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.67179</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.67179</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4126,25 +4120,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>2,9</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.31512</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.31511999999999</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4245,10 +4235,8 @@
           <t>Surya Gubaju</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9851337513</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9851337513</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4267,10 +4255,8 @@
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="inlineStr">
-        <is>
-          <t>9851337513</t>
-        </is>
+      <c r="U17" s="3" t="n">
+        <v>9851337513</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -4287,10 +4273,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.702449</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.702449</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -4324,10 +4308,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH17" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH17" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
@@ -4350,25 +4332,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>CDB181</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.312103</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.31210299999999</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4469,10 +4447,8 @@
           <t>Suyogya Bhandari</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9801056282</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9801056282</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4487,10 +4463,8 @@
       </c>
       <c r="S18" s="3" t="inlineStr"/>
       <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="3" t="inlineStr">
-        <is>
-          <t>9801056282</t>
-        </is>
+      <c r="U18" s="3" t="n">
+        <v>9801056282</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -4507,10 +4481,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.734477</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.734477</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4566,25 +4538,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L3-6</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.338261</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.338261</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4685,10 +4653,8 @@
           <t>Suyogya Bhandari</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9801056282</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9801056282</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4703,10 +4669,8 @@
       </c>
       <c r="S19" s="3" t="inlineStr"/>
       <c r="T19" s="3" t="inlineStr"/>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t>9801056282</t>
-        </is>
+      <c r="U19" s="3" t="n">
+        <v>9801056282</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -4723,10 +4687,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.734477</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.734477</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4782,25 +4744,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>L3-6</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.338261</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.338261</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -532,104 +532,122 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Rajesh Maharjan</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>55.6%</t>
+      <c r="B8" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -644,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -688,42 +706,65 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>83.3%</t>
+      <c r="B4" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>70.8%</t>
         </is>
       </c>
     </row>
@@ -738,16 +779,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,25 +805,30 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -797,19 +844,22 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>12</v>
+      <c r="H2" s="6" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -833,21 +883,24 @@
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Change SSID / Wi-Fi Password</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -856,16 +909,19 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -878,38 +934,128 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="C9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="F9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>15</v>
+      <c r="H9" s="4" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -946,7 +1092,7 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -958,7 +1104,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="26" customWidth="1" min="36" max="36"/>
@@ -969,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4792,6 +4938,1286 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:16 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337429</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Prabin shrestha</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Prabin shrestha</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9823138733</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:16:28 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9823138733</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:39:31 AM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:16:28 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.694908</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>near KUNDAN STORE AND WINE SHOP Tri-Netra Tole, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>ps588355@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>02:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L38-1</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.34301</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>2h 36m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:15 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336972</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Punney Shakya</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Punney Shakya</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9851089473</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:15:13 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9851089473</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 05:00:12 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:15:13 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.66836</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>haktole lukhusi lalitpur ward-7 near Prabhat Higher Secondary School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>shakyapunney@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.32939</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>19h 15m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>5g issue</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337431</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Rachana Sijapati</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Rachana Sijapati</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9803290665</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:49:40 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9803290665</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 09:40:14 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:49:40 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.68831</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur-2,Sanepa, near Naula Bakes, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Change SSID / Wi-Fi Password</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>01:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.30831</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>2h 9m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g issue   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:15 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet showing   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>no internet showing</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336765</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>SANUMAN SHAKYA</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>SANUMAN SHAKYA</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9851053286</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 04:52:47 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9851053286</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 01:59:31 PM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:15:32 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.67933</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Swarnim Tara Vidya Sadan (???????? ???? ??. ??.) M8JQ+3MW, Sahyoginagar Marga, Kathmandu 44600, Bagm</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr"/>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>08:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB256</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.33963</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet showing   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>19h 22m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>22h 16m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet showing   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:14 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet showing   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>no internet showing</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336765</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>SANUMAN SHAKYA</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>SANUMAN SHAKYA</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9851053286</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 04:52:47 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9851053286</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 01:59:31 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:15:32 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.67933</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Swarnim Tara Vidya Sadan (???????? ???? ??. ??.) M8JQ+3MW, Sahyoginagar Marga, Kathmandu 44600, Bagm</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>08:15 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Nirmaya Mukhiya</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB256</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.33963</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet showing   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>19h 22m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>22h 16m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet showing   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335800</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Bir bahadur Mahata</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Bir bahadur Mahata</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9803825206</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:04:45 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>LTP9803825206</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:54:38 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:04:45 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Imadol, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>9803825206@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>17:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB033</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 10m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue    has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5005,10 +5005,8 @@
           <t>Prabin shrestha</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9823138733</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9823138733</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -5043,10 +5041,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>27.694908</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>27.694908</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -5102,25 +5098,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L38-1</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.34301</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.34301000000001</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -5221,10 +5213,8 @@
           <t>Punney Shakya</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9851089473</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9851089473</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5259,10 +5249,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.66836</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.66836</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5314,25 +5302,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>4,9</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.32939</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.32939</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5433,10 +5417,8 @@
           <t>Rachana Sijapati</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9803290665</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9803290665</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5471,10 +5453,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.68831</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.68831</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5526,25 +5506,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.30831</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.30831000000001</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5645,10 +5621,8 @@
           <t>SANUMAN SHAKYA</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9851053286</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9851053286</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5683,10 +5657,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.67933</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.67933</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5738,25 +5710,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>CDB256</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.33963</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.33963</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet showing   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5857,10 +5825,8 @@
           <t>SANUMAN SHAKYA</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9851053286</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9851053286</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5895,10 +5861,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.67933</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.67933</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5950,25 +5914,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB256</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.33963</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.33963</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet showing   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -6069,10 +6029,8 @@
           <t>Bir bahadur Mahata</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9803825206</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9803825206</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6107,10 +6065,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -6166,25 +6122,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB033</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue    has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -586,68 +586,86 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>62.5%</t>
+      <c r="B9" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -706,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>17.9%</t>
         </is>
       </c>
     </row>
@@ -741,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -752,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -779,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -787,9 +805,10 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -820,15 +839,20 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -853,26 +877,29 @@
         <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H2" s="6" t="n">
-        <v>13</v>
+      <c r="H2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I2" s="6" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Change SSID / Wi-Fi Password</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
@@ -886,21 +913,24 @@
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Change SSID / Wi-Fi Password</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -914,18 +944,21 @@
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -940,9 +973,12 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -965,12 +1001,15 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -998,7 +1037,10 @@
       <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1021,41 +1063,78 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="H8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F9" s="4" t="n">
+      <c r="E10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>19</v>
+      <c r="H10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX25"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1115,7 +1194,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6170,6 +6249,850 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:43 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335731</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Bijay khadgi</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Bijay khadgi</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9808318530</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:43:49 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9808318530</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 02:04:55 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:43:49 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.768319</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Tokha Ganeshthan Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>18:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L26-2</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.329818</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 38m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337662</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Bishal dhungana</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Bishal dhungana</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9860377734</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:32:31 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9880213770</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:31:13 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:35:53 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Kadaghari Force park, Lalitpur, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>Vishaldhungana9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>00:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr"/>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Rabindra Bohora</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>4m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336470</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Md Kaif Alam</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Md Kaif Alam</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9818714460</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 10:27:52 AM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>KLK9818714460</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 10:27:52 AM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:47:58 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Dhalkhu , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>kclalita910@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>12:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>CDB517</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 20m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 20m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:46 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336470</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Md Kaif Alam</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Md Kaif Alam</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9818714460</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 10:27:52 AM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>KLK9818714460</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 10:27:52 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:47:58 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Dhalkhu , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>kclalita910@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>12:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>CDB517</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 20m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 20m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.7%</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -923,11 +923,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>1</v>
@@ -954,11 +954,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -1016,11 +1016,11 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
@@ -1047,7 +1047,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1078,11 +1078,11 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1107,34 +1107,96 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="I10" s="4" t="n">
-        <v>22</v>
+      <c r="H12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1148,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX29"/>
+  <dimension ref="A1:AX32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1159,7 +1221,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -1175,7 +1237,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
@@ -6316,10 +6378,8 @@
           <t>Bijay khadgi</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9808318530</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9808318530</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6354,10 +6414,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.768319</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.768319</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -6409,25 +6467,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L26-2</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.329818</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.329818</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -6528,10 +6582,8 @@
           <t>Bishal dhungana</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9860377734</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9860377734</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6566,10 +6618,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -6625,25 +6675,21 @@
           <t>Rabindra Bohora</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6744,10 +6790,8 @@
           <t>Md Kaif Alam</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9818714460</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9818714460</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6837,10 +6881,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -6851,7 +6893,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6952,10 +6994,8 @@
           <t>Md Kaif Alam</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9818714460</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9818714460</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -7045,10 +7085,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -7059,29 +7097,29 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 20m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 20m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 20m</t>
-        </is>
-      </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 20m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7090,6 +7128,630 @@
       <c r="AX29" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:56 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335891</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Khanal</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Kamala Khanal</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9860374577</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:56:06 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860374577</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 03:55:46 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:56:06 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>27.758377612598466, 85.31785862536599, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>ikamalakhanal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>17:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:57 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router adapter damage issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>router adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337213</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Parbata Limbu</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Parbata Limbu</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9763432930</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 08:51:04 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9807992630</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 08:48:41 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:57:35 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t>27.658727,</t>
+        </is>
+      </c>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Near New Bhadrakali Petrol Pump   Mahalaxmi, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>limbuparu40@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>CDB464</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>85.34147</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router adapter damage issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>16h 6m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>16h 8m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : router adapter damage issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:54 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335133</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Mukesh Yadav</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Mukesh Yadav</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9851055106</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:54:06 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9851055106</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>15 Sep 2026 09:06:56 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:54:06 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Lalitpur	Tempo park, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>22:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>4,10</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>2d 15h 47m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -1256,7 +1256,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7198,10 +7198,8 @@
           <t>Kamala Khanal</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9860374577</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9860374577</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -7291,10 +7289,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -7305,7 +7301,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -7406,10 +7402,8 @@
           <t>Parbata Limbu</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9763432930</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9763432930</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -7499,25 +7493,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
           <t>CDB464</t>
         </is>
       </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>85.34147</t>
-        </is>
+      <c r="AP31" s="3" t="n">
+        <v>85.34147</v>
       </c>
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : router adapter damage issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -7618,10 +7608,8 @@
           <t>Mukesh Yadav</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9851055106</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9851055106</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7707,10 +7695,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
@@ -7721,7 +7707,7 @@
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -914,26 +914,26 @@
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -942,23 +942,23 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -1078,11 +1078,11 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -1097,7 +1097,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0</v>
@@ -1109,11 +1109,11 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>9</v>
@@ -1193,10 +1193,10 @@
         <v>4</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1250,13 +1250,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7741,6 +7741,646 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 1:27 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336094</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Rewati Raj Sharma</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Rewati Raj Sharma</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9841757944</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:27:55 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9851151865</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 07:04:23 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:27:55 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.657093</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Near by  kumal hight, Satdobato, Lalitpur 44700, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
+        <is>
+          <t>lutalbhusal22@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>14:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB025</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.330355</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 23m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 1:17 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337477</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Anita lama</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Anita lama</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9823668983</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:07:58 AM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>KLK9823668983</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:07:58 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:17:52 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Bijeshwori, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>9823668983@g.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Change SSID / Wi-Fi Password</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>03:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Mamata Bhujel</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>cdb338</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>3h 9m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>3h 9m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 1:18 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to nettv change  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+      <c r="M35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="inlineStr"/>
+      <c r="O35" s="3" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr"/>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr"/>
+      <c r="V35" s="3" t="inlineStr"/>
+      <c r="W35" s="3" t="inlineStr"/>
+      <c r="X35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr"/>
+      <c r="AA35" s="3" t="inlineStr"/>
+      <c r="AB35" s="3" t="inlineStr"/>
+      <c r="AC35" s="3" t="inlineStr"/>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr"/>
+      <c r="AF35" s="3" t="inlineStr"/>
+      <c r="AG35" s="3" t="inlineStr"/>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr"/>
+      <c r="AM35" s="3" t="inlineStr"/>
+      <c r="AN35" s="3" t="inlineStr"/>
+      <c r="AO35" s="3" t="inlineStr"/>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Skycom to nettv change  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
+      <c r="M36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr"/>
+      <c r="O36" s="3" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr"/>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr"/>
+      <c r="V36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="inlineStr"/>
+      <c r="X36" s="3" t="inlineStr"/>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr"/>
+      <c r="AA36" s="3" t="inlineStr"/>
+      <c r="AB36" s="3" t="inlineStr"/>
+      <c r="AC36" s="3" t="inlineStr"/>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr"/>
+      <c r="AF36" s="3" t="inlineStr"/>
+      <c r="AG36" s="3" t="inlineStr"/>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr"/>
+      <c r="AM36" s="3" t="inlineStr"/>
+      <c r="AN36" s="3" t="inlineStr"/>
+      <c r="AO36" s="3" t="inlineStr"/>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>18.9%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>2</v>
@@ -1196,7 +1196,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX36"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1240,7 +1240,7 @@
     <col width="13" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -7808,10 +7808,8 @@
           <t>Rewati Raj Sharma</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9841757944</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9841757944</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7905,25 +7903,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>CDB025</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.330355</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.330355</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -8024,10 +8018,8 @@
           <t>Anita lama</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9823668983</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9823668983</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -8117,10 +8109,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -8131,7 +8121,7 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -8381,6 +8371,438 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 1:44 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336457</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Prajapati</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Sanjay Prajapati</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9841972051</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:44:35 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9841972051</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 10:20:17 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:44:35 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.677836</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>Bhatkya Pati Gift Shop - Gift shop MCHV+Q2H Bhaktapur 44800, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>Jay.sanpjpt@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>13:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>L15-5</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.443087</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 24m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 1:33 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336930</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Bhattarai</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Bhattarai</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9841054815</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 04:34:40 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9841054815</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 04:34:40 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:33:47 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.68306</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Sankhamul,Shreenagar ,Side of Lumbini Resunga Electric Center,Ward -31,Kathmandu, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>nirajanread@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>06:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB165</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.33647</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>20h 59m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>20h 59m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1187,7 +1187,7 @@
         <v>9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>4</v>
@@ -1196,7 +1196,7 @@
         <v>5</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8438,10 +8438,8 @@
           <t>Sanjay Prajapati</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9841972051</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9841972051</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8535,25 +8533,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>L15-5</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.443087</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.44308700000001</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -8654,10 +8648,8 @@
           <t>Nirajan Bhattarai</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9841054815</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9841054815</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8751,47 +8743,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB165</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.33647</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.33647000000001</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>20h 59m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>20h 59m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>20h 59m</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>20h 59m</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV38" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -8800,6 +8788,214 @@
       <c r="AX38" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:01 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335936</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Gopi Krishna Aryal</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Gopi Krishna Aryal</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9848488998</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:01:52 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9848488998</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 04:52:00 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:01:52 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Shree Prithvi Narayan Secondary School - Government school Q75Q+QVG Tarakeshwar 44600 - Shree Prithv</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>gopi.aryal1984@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>17:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>L50-6</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 9m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>69.0%</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>19.0%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -880,13 +880,13 @@
         <v>3</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>2</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>3</v>
@@ -1190,13 +1190,13 @@
         <v>3</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>5</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX39"/>
+  <dimension ref="A1:AX43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8858,10 +8858,8 @@
           <t>Gopi Krishna Aryal</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9848488998</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9848488998</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8951,10 +8949,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -8965,37 +8961,893 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 9m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 Router   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:13 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337676</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Avani Foods Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Avani Foods Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9851329400</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:13:07 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9851335270</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 12:42:37 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:13:07 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.690911</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>M8R9+85J, Maternity Hospital Road, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>avani.aarogya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>01:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.317616</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h 9m</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>1h 30m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 Router   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW39" s="3" t="inlineStr">
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX39" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:13 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336711</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Air Care Service Center</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Bandan Sampang Rai</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9807951781</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:14:11 AM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9807951781</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 01:26:48 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:13:37 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.73474</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Rato Pul - Bridge P85P+6PG Pashupati Sadak Kathmandu 44600, , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>bandan.kirati@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr"/>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>L5-1</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.35697</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>3h 59m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 46m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337234</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Suman Acharya</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Suman Acharya</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9861661951</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 09:21:49 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9810150201</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 09:21:49 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:07:15 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.67762</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor Near Near  Facebook food and coffee Shuvakamana Marg, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>sumnac2@gmail.Com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>04:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>3,10</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.34133</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>16h 45m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>16h 45m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336753</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Sabita karanjit</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Sabita karanjit</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9860200274</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:11:07 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9860200274</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 01:54:18 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:11:07 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.679178</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Kamalbinayak film hall, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>10:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L45-3</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.436081</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 16m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -877,16 +877,16 @@
         <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1187,16 +1187,16 @@
         <v>9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX43"/>
+  <dimension ref="A1:AX46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9062,10 +9062,8 @@
           <t>Avani Foods Pvt Ltd</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9851329400</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9851329400</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -9159,25 +9157,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>1,8</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.317616</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.317616</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -9278,10 +9272,8 @@
           <t>Bandan Sampang Rai</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9807951781</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9807951781</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -9371,25 +9363,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>L5-1</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.35697</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.35697</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -9490,10 +9478,8 @@
           <t>Suman Acharya</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9861661951</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9861661951</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -9587,25 +9573,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>3,10</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.34133</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.34133</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -9696,20 +9678,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="3" t="inlineStr">
         <is>
           <t>Sabita karanjit</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9860200274</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9860200274</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9799,55 +9775,703 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L45-3</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.436081</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.436081</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>1d 16m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:31 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337212</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Bharti</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Niraj Bharti</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9803165887</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:31:24 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>9803165887</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 08:48:14 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:31:24 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu - Tokha Dhaneshwor Mandir - 3month(150Mbps)-Enquiry, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>bharatiniraj111@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>L9-4</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>1d 16m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>17h 43m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:23 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337520</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Ghale</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Ghale</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9862565015</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX43" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:31:58 AM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9862565015</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:31:58 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:23:23 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.71321</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Hasantar Nunnery, Karma Ngedon Osel Choekhorling.P67X+7HG, Puldol Rd, Nagarjun 44600, Bagmati, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>sntsghale@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>03:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.25017</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:22 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337520</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Ghale</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Ghale</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9862565015</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:31:58 AM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9862565015</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:31:58 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:23:23 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.71321</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Hasantar Nunnery, Karma Ngedon Osel Choekhorling.P67X+7HG, Puldol Rd, Nagarjun 44600, Bagmati, Nepal</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>sntsghale@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>03:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.25017</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -954,17 +954,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -973,23 +973,23 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -1016,7 +1016,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>1</v>
@@ -1047,7 +1047,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1078,7 +1078,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>1</v>
@@ -1181,7 +1181,7 @@
         <v>3</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>9</v>
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX46"/>
+  <dimension ref="A1:AX47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1237,7 +1237,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="21" customWidth="1" min="28" max="28"/>
@@ -1254,7 +1254,7 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
     <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
@@ -9890,10 +9890,8 @@
           <t>Niraj Bharti</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9803165887</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9803165887</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9983,25 +9981,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>L9-4</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -10102,10 +10096,8 @@
           <t>Santosh Ghale</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9862565015</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9862565015</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -10181,10 +10173,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH45" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH45" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
@@ -10203,25 +10193,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.25017</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.25017</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -10322,10 +10308,8 @@
           <t>Santosh Ghale</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9862565015</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9862565015</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -10401,10 +10385,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH46" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH46" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
@@ -10423,47 +10405,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.25017</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.25017</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>3h 51m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS46" s="3" t="inlineStr">
-        <is>
-          <t>3h 51m</t>
-        </is>
-      </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>3h 51m</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV46" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -10472,6 +10450,226 @@
       <c r="AX46" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:39 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replace  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>Router replace</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336001</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Shrestha</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Sujan Shrestha</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9848505695</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:39:42 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>LTP9848505695</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 05:35:31 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:39:42 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.63426547568562</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>lalitpur harisiddhi tralee mart, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>dgt6@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>17:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.3411102294922</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replace  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 4m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replace  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.2%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -886,7 +886,7 @@
         <v>4</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1178,7 +1178,7 @@
         <v>4</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>4</v>
@@ -1196,7 +1196,7 @@
         <v>6</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX47"/>
+  <dimension ref="A1:AX48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10520,10 +10520,8 @@
           <t>Sujan Shrestha</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9848505695</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9848505695</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -10599,10 +10597,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH47" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH47" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
@@ -10621,55 +10617,259 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>3,1</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.3411102294922</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.3411102294922</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 4m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
           <t>Case : Router replace  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS47" s="3" t="inlineStr">
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1332671</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Rajkumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Rajkumar Chaudhary</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9746841107</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:56:05 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>LTP9746841107</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>13 Sep 2026 03:58:30 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 02:56:05 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Sahid Smarak Park M8Q2+8GM, Lalitpur 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>20:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT47" s="3" t="inlineStr">
-        <is>
-          <t>1d 21h 4m</t>
-        </is>
-      </c>
-      <c r="AU47" s="3" t="inlineStr">
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>4d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV47" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router replace  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW47" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX47" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>33</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>21</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>64.0%</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
@@ -886,23 +886,23 @@
         <v>4</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Change SSID / Wi-Fi Password</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>2</v>
@@ -923,17 +923,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Change SSID / Wi-Fi Password</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>2</v>
@@ -954,7 +954,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -1016,11 +1016,11 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0</v>
@@ -1047,7 +1047,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1078,7 +1078,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>1</v>
@@ -1109,11 +1109,11 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>1</v>
@@ -1140,11 +1140,11 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>0</v>
@@ -1169,34 +1169,65 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B13" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="G13" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="I12" s="4" t="n">
-        <v>36</v>
+      <c r="I13" s="4" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX48"/>
+  <dimension ref="A1:AX51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -10732,10 +10763,8 @@
           <t>Rajkumar Chaudhary</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9746841107</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9746841107</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10825,10 +10854,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
@@ -10839,37 +10866,661 @@
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>4d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS48" s="3" t="inlineStr">
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:15 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>stb issue</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336996</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Kafle</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Kafle</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9846108667</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 05:48:49 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9846108667</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 05:25:16 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:15:37 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.68558</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Kritipur Maitinagar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr"/>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>CDB457</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.277263</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>21h 26m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>21h 50m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:09 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337743</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Mina Rakaskoti</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Mina Rakaskoti</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9706418933</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:13:34 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>CHB9706418933</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:35:44 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:13:34 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Besi Gaun Gokarneshwor 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>sushanimagar00@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>L15-4</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT48" s="3" t="inlineStr">
-        <is>
-          <t>4d 22h 57m</t>
-        </is>
-      </c>
-      <c r="AU48" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV48" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW48" s="3" t="inlineStr">
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1h 37m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX48" s="3" t="inlineStr">
-        <is>
-          <t>Chandramani Tharu</t>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:05 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1335308</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Nabaraj Pokharel</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:14:39 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9851042928</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 08:59:52 AM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:14:39 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.7709</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Hello Kids Academy Montessori School Details from Google Maps Q9C3+32Q, Budhanilkantha 44600 , Bagma</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>pokharelnaba1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr"/>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Rikesh Shrestha</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L15-8</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.3504</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 14m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -892,17 +892,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0</v>
@@ -985,17 +985,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -1004,19 +1004,19 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -1209,7 +1209,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>4</v>
@@ -1227,7 +1227,7 @@
         <v>6</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX51"/>
+  <dimension ref="A1:AX53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1281,7 +1281,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -10967,10 +10967,8 @@
           <t>Ramesh Kafle</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9846108667</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9846108667</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -11056,25 +11054,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>CDB457</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.277263</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.277263</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : stb issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
@@ -11175,10 +11169,8 @@
           <t>Mina Rakaskoti</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9706418933</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9706418933</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -11264,10 +11256,8 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
@@ -11278,7 +11268,7 @@
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -11379,10 +11369,8 @@
           <t>Nabaraj Pokharel</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9851042928</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9851042928</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -11472,55 +11460,375 @@
           <t>Rikesh Shrestha</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>L15-8</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.3504</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.35039999999999</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>2d 6h 14m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:31 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr"/>
+      <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="inlineStr"/>
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr"/>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr"/>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr"/>
+      <c r="V52" s="3" t="inlineStr"/>
+      <c r="W52" s="3" t="inlineStr"/>
+      <c r="X52" s="3" t="inlineStr"/>
+      <c r="Y52" s="3" t="inlineStr"/>
+      <c r="Z52" s="3" t="inlineStr"/>
+      <c r="AA52" s="3" t="inlineStr"/>
+      <c r="AB52" s="3" t="inlineStr"/>
+      <c r="AC52" s="3" t="inlineStr"/>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr"/>
+      <c r="AF52" s="3" t="inlineStr"/>
+      <c r="AG52" s="3" t="inlineStr"/>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr"/>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr"/>
+      <c r="AM52" s="3" t="inlineStr"/>
+      <c r="AN52" s="3" t="inlineStr"/>
+      <c r="AO52" s="3" t="inlineStr"/>
+      <c r="AP52" s="3" t="inlineStr"/>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:25 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV SETBOX   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV SETBOX</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337553</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Rohit Kumar</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Rohit Kumar</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9841338373</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:25:17 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841338373</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:01:19 AM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:25:17 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Kuleshor hanuman mandir, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>9841338373@g.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>04:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>CDB137</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV SETBOX   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>2d 6h 14m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW51" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX51" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>4h 23m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV SETBOX   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -883,41 +883,41 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -985,17 +985,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>9</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX53"/>
+  <dimension ref="A1:AX57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11683,10 +11683,8 @@
           <t>Rohit Kumar</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9841338373</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9841338373</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -11780,55 +11778,899 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>CDB137</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>4h 23m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV SETBOX   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS53" s="3" t="inlineStr">
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:37 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>router damage</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337556</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Bhujel</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Madhav Bhujel</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9863360379</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:44:53 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9863360379</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:02:31 AM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:44:53 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr">
+        <is>
+          <t>27.743268</t>
+        </is>
+      </c>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Manamaiju , Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr"/>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>L45-7</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr">
+        <is>
+          <t>85.312923</t>
+        </is>
+      </c>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT53" s="3" t="inlineStr">
-        <is>
-          <t>4h 23m</t>
-        </is>
-      </c>
-      <c r="AU53" s="3" t="inlineStr">
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>4h 42m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:39 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337549</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Shrestha</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Shrestha</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9843592437</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:57:53 AM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9843592437</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:57:53 AM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:39:30 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.710813</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>near Kumari Temple Nagarjun , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr"/>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>04:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.272312</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>4h 41m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>4h 41m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:38 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337549</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Shrestha</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Mohan Shrestha</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9843592437</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:57:53 AM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9843592437</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:57:53 AM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:39:30 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr">
+        <is>
+          <t>27.710813</t>
+        </is>
+      </c>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>near Kumari Temple Nagarjun , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr"/>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr"/>
+      <c r="AI56" s="3" t="inlineStr">
+        <is>
+          <t>04:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>85.272312</t>
+        </is>
+      </c>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>4h 41m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>4h 41m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:32 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : router adapter damage issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>router adapter damage issue</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337213</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Parbata Limbu</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Parbata Limbu</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9763432930</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>9807992630</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 08:48:41 PM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:32:03 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.658727,</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Near New Bhadrakali Petrol Pump   Mahalaxmi, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>limbuparu40@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr">
+        <is>
+          <t>05:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>CDB464</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.34147</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : router adapter damage issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>18h 43m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV53" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV SETBOX   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW53" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX53" s="3" t="inlineStr">
-        <is>
-          <t>Chandramani Tharu</t>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : router adapter damage issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.5%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>20.7%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>62.1%</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
@@ -886,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1218,7 +1218,7 @@
         <v>9</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>5</v>
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX57"/>
+  <dimension ref="A1:AX59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11893,10 +11893,8 @@
           <t>Madhav Bhujel</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9863360379</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9863360379</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11982,25 +11980,21 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
           <t>L45-7</t>
         </is>
       </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>85.312923</t>
-        </is>
+      <c r="AP54" s="3" t="n">
+        <v>85.312923</v>
       </c>
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : router damage  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -12101,10 +12095,8 @@
           <t>Mohan Shrestha</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9843592437</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9843592437</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -12194,25 +12186,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.272312</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.272312</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -12313,10 +12301,8 @@
           <t>Mohan Shrestha</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9843592437</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9843592437</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -12406,25 +12392,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP56" s="3" t="inlineStr">
-        <is>
-          <t>85.272312</t>
-        </is>
+      <c r="AP56" s="3" t="n">
+        <v>85.272312</v>
       </c>
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
@@ -12525,10 +12507,8 @@
           <t>Parbata Limbu</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9763432930</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9763432930</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -12622,55 +12602,471 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>CDB464</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.34147</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.34147</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>18h 43m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
           <t>Case : router adapter damage issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS57" s="3" t="inlineStr">
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:55 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337743</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Mina Rakaskoti</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Mina Rakaskoti</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9706418933</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:55:08 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>CHB9706418933</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 01:35:44 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:55:08 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Besi Gaun Gokarneshwor 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>sushanimagar00@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr"/>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>L15-4</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr"/>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT57" s="3" t="inlineStr">
-        <is>
-          <t>18h 43m</t>
-        </is>
-      </c>
-      <c r="AU57" s="3" t="inlineStr">
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>2h 19m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 3:51 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336668</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>Milan Pyakurel</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>Milan Pyakurel</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9813451987</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:51:47 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9813451987</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 12:51:08 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:51:47 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.73113</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu ,BasunDhara-3,Near BP Hodpital, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>milanpyakurel9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr"/>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>13:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>L34-8</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.33138</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV57" s="3" t="inlineStr">
-        <is>
-          <t>Case : router adapter damage issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW57" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX57" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.7%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.7%</t>
         </is>
       </c>
     </row>
@@ -880,13 +880,13 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -1221,13 +1221,13 @@
         <v>7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>7</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX59"/>
+  <dimension ref="A1:AX61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -12717,10 +12717,8 @@
           <t>Mina Rakaskoti</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9706418933</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9706418933</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -12806,10 +12804,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
@@ -12820,7 +12816,7 @@
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -12921,10 +12917,8 @@
           <t>Milan Pyakurel</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9813451987</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9813451987</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -13018,55 +13012,479 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>L34-8</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.33138</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.33138</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS59" s="3" t="inlineStr">
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 4:14 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336976</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Moktan</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Moktan</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9810308110</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:14:27 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9810308110</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 05:08:12 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:14:27 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>27.676315</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>The Celebration Co-Ed - School Gothatar, Kageshwori Manohara 8 Kathmandu 44600, Kathmandu, Nepal, Ne</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr"/>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr"/>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>09:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>1,11</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>85.329125</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT59" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h</t>
-        </is>
-      </c>
-      <c r="AU59" s="3" t="inlineStr">
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>23h 6m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV59" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW59" s="3" t="inlineStr">
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX60" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 4:12 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336972</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Punney Shakya</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Punney Shakya</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9851089473</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:12:49 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>9851089473</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 05:00:12 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:12:49 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr">
+        <is>
+          <t>27.66836</t>
+        </is>
+      </c>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>haktole lukhusi lalitpur ward-7 near Prabhat Higher Secondary School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr">
+        <is>
+          <t>shakyapunney@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr"/>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>09:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>4,9</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr">
+        <is>
+          <t>85.32939</t>
+        </is>
+      </c>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>23h 12m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX59" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX61" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>92.3%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -883,10 +883,10 @@
         <v>2</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>5</v>
@@ -1224,10 +1224,10 @@
         <v>6</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX61"/>
+  <dimension ref="A1:AX64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -13127,10 +13127,8 @@
           <t>Manisha Moktan</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9810308110</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9810308110</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -13220,25 +13218,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>85.329125</t>
-        </is>
+      <c r="AP60" s="3" t="n">
+        <v>85.329125</v>
       </c>
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
@@ -13339,10 +13333,8 @@
           <t>Punney Shakya</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9851089473</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9851089473</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -13436,47 +13428,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
           <t>4,9</t>
         </is>
       </c>
-      <c r="AP61" s="3" t="inlineStr">
-        <is>
-          <t>85.32939</t>
-        </is>
+      <c r="AP61" s="3" t="n">
+        <v>85.32939</v>
       </c>
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>23h 12m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS61" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT61" s="3" t="inlineStr">
-        <is>
-          <t>23h 12m</t>
-        </is>
-      </c>
-      <c r="AU61" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV61" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW61" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -13485,6 +13473,618 @@
       <c r="AX61" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 4:21 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337488</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Rai</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Rai</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>9849225414</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:15:07 AM</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>9849225414</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:13:57 AM</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:21:37 PM</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr"/>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr">
+        <is>
+          <t>Blue Wren International School - International school M7XG+Q7C Kathmandu 44600, Bagmati, Nepal, Nepa</t>
+        </is>
+      </c>
+      <c r="AF62" s="3" t="inlineStr"/>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr"/>
+      <c r="AI62" s="3" t="inlineStr">
+        <is>
+          <t>06:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>CDB206</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr"/>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>6h 6m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>6h 7m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 4:20 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337488</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Rai</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Bishal Rai</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9849225414</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:15:07 AM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>9849225414</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:13:57 AM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:21:37 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr"/>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>Blue Wren International School - International school M7XG+Q7C Kathmandu 44600, Bagmati, Nepal, Nepa</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr"/>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr">
+        <is>
+          <t>06:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>CDB206</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr"/>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>6h 6m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>6h 7m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX63" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 4:21 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337631</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Samser bisunke</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Samser bisunke</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9840247451</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:51:26 AM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>9840247451</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:51:26 AM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:21:46 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr"/>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>Near police station, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr"/>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr"/>
+      <c r="AI64" s="3" t="inlineStr">
+        <is>
+          <t>04:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>4,3</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr"/>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX64" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>43</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>27</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -880,13 +880,13 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -1221,13 +1221,13 @@
         <v>7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX64"/>
+  <dimension ref="A1:AX65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -13543,10 +13543,8 @@
           <t>Bishal Rai</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>9849225414</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>9849225414</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -13632,10 +13630,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN62" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
@@ -13646,7 +13642,7 @@
       <c r="AQ62" s="3" t="inlineStr"/>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
@@ -13747,10 +13743,8 @@
           <t>Bishal Rai</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9849225414</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9849225414</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -13836,10 +13830,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
@@ -13850,7 +13842,7 @@
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
@@ -13951,10 +13943,8 @@
           <t>Samser bisunke</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9840247451</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9840247451</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -14040,10 +14030,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
@@ -14054,29 +14042,29 @@
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>4h 30m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS64" s="3" t="inlineStr">
-        <is>
-          <t>4h 30m</t>
-        </is>
-      </c>
-      <c r="AT64" s="3" t="inlineStr">
-        <is>
-          <t>4h 30m</t>
-        </is>
-      </c>
-      <c r="AU64" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV64" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW64" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -14085,6 +14073,210 @@
       <c r="AX64" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 4:39 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336234</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Sandip Tamang</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>Sandip Tamang</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9813373038</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:46:21 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>9813373038</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>16 Sep 2026 09:46:21 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:39:44 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr"/>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>Suryodaya Sai Eng. School Mahalaxmi 44600101, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr">
+        <is>
+          <t>stmg9642@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr"/>
+      <c r="AI65" s="3" t="inlineStr"/>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr"/>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 53m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 53m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX65" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.7%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.1%</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>2</v>
@@ -886,7 +886,7 @@
         <v>6</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -1209,7 +1209,7 @@
         <v>6</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>4</v>
@@ -1227,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX65"/>
+  <dimension ref="A1:AX66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1254,10 +1254,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -14143,10 +14143,8 @@
           <t>Sandip Tamang</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9813373038</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9813373038</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -14232,10 +14230,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
@@ -14246,29 +14242,29 @@
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 53m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 53m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS65" s="3" t="inlineStr">
-        <is>
-          <t>1d 18h 53m</t>
-        </is>
-      </c>
-      <c r="AT65" s="3" t="inlineStr">
-        <is>
-          <t>1d 18h 53m</t>
-        </is>
-      </c>
-      <c r="AU65" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV65" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW65" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -14277,6 +14273,214 @@
       <c r="AX65" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 4:55 PM</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>wifi6 router</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337873</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Ghandruk Hydropower Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>Ghandruk Hydropower Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>9849070756</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:55:04 PM</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849070756</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 03:05:29 PM</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 04:55:04 PM</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y66" s="3" t="inlineStr"/>
+      <c r="Z66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB66" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC66" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="inlineStr"/>
+      <c r="AE66" s="3" t="inlineStr">
+        <is>
+          <t>27.683822, 85.323786, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF66" s="3" t="inlineStr">
+        <is>
+          <t>9849070756@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH66" s="3" t="inlineStr"/>
+      <c r="AI66" s="3" t="inlineStr">
+        <is>
+          <t>01:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ66" s="3" t="inlineStr"/>
+      <c r="AK66" s="3" t="inlineStr"/>
+      <c r="AL66" s="3" t="inlineStr">
+        <is>
+          <t>Laxmi Karki</t>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO66" s="3" t="inlineStr">
+        <is>
+          <t>2,12</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr"/>
+      <c r="AQ66" s="3" t="inlineStr"/>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>1h 49m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6 router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX66" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>93.3%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>69.6%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.3%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -877,16 +877,16 @@
         <v>8</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1218,16 +1218,16 @@
         <v>9</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX66"/>
+  <dimension ref="A1:AX70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -14343,10 +14343,8 @@
           <t>Ghandruk Hydropower Pvt Ltd</t>
         </is>
       </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>9849070756</t>
-        </is>
+      <c r="O66" s="3" t="n">
+        <v>9849070756</v>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
@@ -14436,10 +14434,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN66" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN66" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
@@ -14450,37 +14446,897 @@
       <c r="AQ66" s="3" t="inlineStr"/>
       <c r="AR66" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>1h 49m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6 router  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS66" s="3" t="inlineStr">
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX66" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 5:12 PM</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337627</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Rakchhya Karki</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>Rakchhya Karki</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>9849876657</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:12:19 PM</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>9847618458</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:49:20 AM</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:12:19 PM</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr"/>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD67" s="3" t="inlineStr"/>
+      <c r="AE67" s="3" t="inlineStr">
+        <is>
+          <t>Near to Hattigauda Bus Stop - Bus stop Khadka Bhadrakali Rd Budhanilkantha , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF67" s="3" t="inlineStr">
+        <is>
+          <t>raksha.karki218@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="inlineStr"/>
+      <c r="AI67" s="3" t="inlineStr">
+        <is>
+          <t>05:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ67" s="3" t="inlineStr"/>
+      <c r="AK67" s="3" t="inlineStr"/>
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>L57-8</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr"/>
+      <c r="AQ67" s="3" t="inlineStr"/>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT66" s="3" t="inlineStr">
-        <is>
-          <t>1h 49m</t>
-        </is>
-      </c>
-      <c r="AU66" s="3" t="inlineStr">
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>5h 22m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV66" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6 router  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW66" s="3" t="inlineStr">
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX66" s="3" t="inlineStr">
-        <is>
-          <t>Chandramani Tharu</t>
+      <c r="AX67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 5:06 PM</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337590</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Shubham Bikram Shah</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>Shubham Bikram Shah</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>9821232022</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:06:12 PM</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>9821232022</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:21:22 AM</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:06:12 PM</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr">
+        <is>
+          <t>27.650111</t>
+        </is>
+      </c>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="inlineStr"/>
+      <c r="AE68" s="3" t="inlineStr">
+        <is>
+          <t>Imdole Near  New Millennium School , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF68" s="3" t="inlineStr">
+        <is>
+          <t>shuvam.vikram@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI68" s="3" t="inlineStr">
+        <is>
+          <t>05:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ68" s="3" t="inlineStr"/>
+      <c r="AK68" s="3" t="inlineStr"/>
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>L60-7</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr">
+        <is>
+          <t>85.348817</t>
+        </is>
+      </c>
+      <c r="AQ68" s="3" t="inlineStr"/>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>5h 44m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX68" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 5:11 PM</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337601</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Suraj Dangal</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Suraj Dangal</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>9840290000</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:30:04 AM</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr">
+        <is>
+          <t>9849423777G</t>
+        </is>
+      </c>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:30:04 AM</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:11:09 PM</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y69" s="3" t="inlineStr">
+        <is>
+          <t>27.68476</t>
+        </is>
+      </c>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD69" s="3" t="inlineStr"/>
+      <c r="AE69" s="3" t="inlineStr">
+        <is>
+          <t>Satungal,Chandragiri ,near Nepal Electricity Authority, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF69" s="3" t="inlineStr">
+        <is>
+          <t>surajdangal1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="inlineStr"/>
+      <c r="AI69" s="3" t="inlineStr">
+        <is>
+          <t>05:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ69" s="3" t="inlineStr"/>
+      <c r="AK69" s="3" t="inlineStr"/>
+      <c r="AL69" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>CDB283</t>
+        </is>
+      </c>
+      <c r="AP69" s="3" t="inlineStr">
+        <is>
+          <t>85.24633</t>
+        </is>
+      </c>
+      <c r="AQ69" s="3" t="inlineStr"/>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
+        <is>
+          <t>5h 41m</t>
+        </is>
+      </c>
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>5h 41m</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX69" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 5:10 PM</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337601</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Suraj Dangal</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>Suraj Dangal</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>9840290000</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:30:04 AM</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="3" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr">
+        <is>
+          <t>9849423777G</t>
+        </is>
+      </c>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 11:30:04 AM</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:11:09 PM</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y70" s="3" t="inlineStr">
+        <is>
+          <t>27.68476</t>
+        </is>
+      </c>
+      <c r="Z70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA70" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB70" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC70" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD70" s="3" t="inlineStr"/>
+      <c r="AE70" s="3" t="inlineStr">
+        <is>
+          <t>Satungal,Chandragiri ,near Nepal Electricity Authority, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF70" s="3" t="inlineStr">
+        <is>
+          <t>surajdangal1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG70" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH70" s="3" t="inlineStr"/>
+      <c r="AI70" s="3" t="inlineStr">
+        <is>
+          <t>05:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ70" s="3" t="inlineStr"/>
+      <c r="AK70" s="3" t="inlineStr"/>
+      <c r="AL70" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN70" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO70" s="3" t="inlineStr">
+        <is>
+          <t>CDB283</t>
+        </is>
+      </c>
+      <c r="AP70" s="3" t="inlineStr">
+        <is>
+          <t>85.24633</t>
+        </is>
+      </c>
+      <c r="AQ70" s="3" t="inlineStr"/>
+      <c r="AR70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>5h 41m</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>5h 41m</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
@@ -886,7 +886,7 @@
         <v>7</v>
       </c>
       <c r="I2" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -1206,7 +1206,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>6</v>
@@ -1227,7 +1227,7 @@
         <v>9</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX70"/>
+  <dimension ref="A1:AX71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -14547,10 +14547,8 @@
           <t>Rakchhya Karki</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>9849876657</t>
-        </is>
+      <c r="O67" s="3" t="n">
+        <v>9849876657</v>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
@@ -14640,10 +14638,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN67" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN67" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
@@ -14654,7 +14650,7 @@
       <c r="AQ67" s="3" t="inlineStr"/>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
@@ -14755,10 +14751,8 @@
           <t>Shubham Bikram Shah</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>9821232022</t>
-        </is>
+      <c r="O68" s="3" t="n">
+        <v>9821232022</v>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
@@ -14834,10 +14828,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH68" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH68" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI68" s="3" t="inlineStr">
         <is>
@@ -14856,25 +14848,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN68" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
           <t>L60-7</t>
         </is>
       </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>85.348817</t>
-        </is>
+      <c r="AP68" s="3" t="n">
+        <v>85.348817</v>
       </c>
       <c r="AQ68" s="3" t="inlineStr"/>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
@@ -14975,10 +14963,8 @@
           <t>Suraj Dangal</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>9840290000</t>
-        </is>
+      <c r="O69" s="3" t="n">
+        <v>9840290000</v>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
@@ -15072,25 +15058,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN69" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN69" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
           <t>CDB283</t>
         </is>
       </c>
-      <c r="AP69" s="3" t="inlineStr">
-        <is>
-          <t>85.24633</t>
-        </is>
+      <c r="AP69" s="3" t="n">
+        <v>85.24633</v>
       </c>
       <c r="AQ69" s="3" t="inlineStr"/>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
@@ -15191,10 +15173,8 @@
           <t>Suraj Dangal</t>
         </is>
       </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>9840290000</t>
-        </is>
+      <c r="O70" s="3" t="n">
+        <v>9840290000</v>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
@@ -15288,55 +15268,263 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN70" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN70" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
           <t>CDB283</t>
         </is>
       </c>
-      <c r="AP70" s="3" t="inlineStr">
-        <is>
-          <t>85.24633</t>
-        </is>
+      <c r="AP70" s="3" t="n">
+        <v>85.24633</v>
       </c>
       <c r="AQ70" s="3" t="inlineStr"/>
       <c r="AR70" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>5h 41m</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>5h 41m</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS70" s="3" t="inlineStr">
-        <is>
-          <t>5h 41m</t>
-        </is>
-      </c>
-      <c r="AT70" s="3" t="inlineStr">
-        <is>
-          <t>5h 41m</t>
-        </is>
-      </c>
-      <c r="AU70" s="3" t="inlineStr">
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX70" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 5:17 PM</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>TKT1337512</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Shrestha</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Prakash Shrestha</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>9808592408</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:26:47 AM</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="3" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>9808592408</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 10:26:47 AM</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 05:17:52 PM</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr">
+        <is>
+          <t>27.675275</t>
+        </is>
+      </c>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA71" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB71" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC71" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD71" s="3" t="inlineStr"/>
+      <c r="AE71" s="3" t="inlineStr">
+        <is>
+          <t>dalpa puspa sadan school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF71" s="3" t="inlineStr"/>
+      <c r="AG71" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH71" s="3" t="inlineStr"/>
+      <c r="AI71" s="3" t="inlineStr">
+        <is>
+          <t>06:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ71" s="3" t="inlineStr"/>
+      <c r="AK71" s="3" t="inlineStr"/>
+      <c r="AL71" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>85.272686</t>
+        </is>
+      </c>
+      <c r="AQ71" s="3" t="inlineStr"/>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>6h 51m</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>6h 51m</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV70" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW70" s="3" t="inlineStr">
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX70" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
+      <c r="AX71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -1287,7 +1287,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -15383,10 +15383,8 @@
           <t>Prakash Shrestha</t>
         </is>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>9808592408</t>
-        </is>
+      <c r="O71" s="3" t="n">
+        <v>9808592408</v>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
@@ -15476,25 +15474,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN71" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
           <t>3,3</t>
         </is>
       </c>
-      <c r="AP71" s="3" t="inlineStr">
-        <is>
-          <t>85.272686</t>
-        </is>
+      <c r="AP71" s="3" t="n">
+        <v>85.27268599999999</v>
       </c>
       <c r="AQ71" s="3" t="inlineStr"/>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -658,14 +658,14 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -724,19 +724,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX71"/>
+  <dimension ref="A1:AX72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1287,7 +1287,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -15522,6 +15522,218 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 6:24 PM</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>stb issue</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1336996</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Kafle</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Kafle</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>9846108667</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 06:24:04 PM</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="3" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>9846108667</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>17 Sep 2026 05:25:16 PM</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026 06:24:04 PM</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr">
+        <is>
+          <t>27.68558</t>
+        </is>
+      </c>
+      <c r="Z72" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA72" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB72" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC72" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD72" s="3" t="inlineStr"/>
+      <c r="AE72" s="3" t="inlineStr">
+        <is>
+          <t>Kritipur Maitinagar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF72" s="3" t="inlineStr"/>
+      <c r="AG72" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH72" s="3" t="inlineStr"/>
+      <c r="AI72" s="3" t="inlineStr">
+        <is>
+          <t>10:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ72" s="3" t="inlineStr"/>
+      <c r="AK72" s="3" t="inlineStr"/>
+      <c r="AL72" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO72" s="3" t="inlineStr">
+        <is>
+          <t>CDB457</t>
+        </is>
+      </c>
+      <c r="AP72" s="3" t="inlineStr">
+        <is>
+          <t>85.277263</t>
+        </is>
+      </c>
+      <c r="AQ72" s="3" t="inlineStr"/>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>1d 58m</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
+          <t>Case : stb issue  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_18_Sep_2026.xlsx
@@ -1287,7 +1287,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="19" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -15589,10 +15589,8 @@
           <t>Ramesh Kafle</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>9846108667</t>
-        </is>
+      <c r="O72" s="3" t="n">
+        <v>9846108667</v>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
@@ -15682,25 +15680,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN72" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN72" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
           <t>CDB457</t>
         </is>
       </c>
-      <c r="AP72" s="3" t="inlineStr">
-        <is>
-          <t>85.277263</t>
-        </is>
+      <c r="AP72" s="3" t="n">
+        <v>85.277263</v>
       </c>
       <c r="AQ72" s="3" t="inlineStr"/>
       <c r="AR72" s="3" t="inlineStr">
         <is>
-          <t>Case : stb issue  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS72" s="3" t="inlineStr">
